--- a/data/Issued_Project_Documents.xlsx
+++ b/data/Issued_Project_Documents.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F64"/>
+  <dimension ref="A1:F62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,1246 +451,1246 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Concept</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00004-TRA242-20241127</t>
+          <t>Costa Rica-TREES-Concept-Final-Dec12</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2020-12-21</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Concept</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00004-TRA242-20241127</t>
+          <t>DM-0402-2020 Mrs. Mary Grady</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2020-12-21</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00004-TRA242-20241127</t>
+          <t>Translated Document Disclaimer</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2026-04-30</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Monitoring Report - Verified</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Program Documentation</t>
+          <t>2017-2019 TREES-Monitoring-Report-Costa Rica-Verified</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Opinion</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Program Documentation</t>
+          <t>2017-2019 TREES-Verification-Opinion-Costa Rica_Final_2026-06-15</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Report</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Program Documentation</t>
+          <t>2017-2019 TREES-Verification-Report-Costa Rica_Final_2026-06-15</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2024-12-03</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Registration Document - Validated</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Costa Rica ERPD EN_Oct24-2018_clean</t>
+          <t>2017-2021 TREES-Registration-Document-Costa Rica-Validated</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0101</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Costa Rica</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>100000</v>
+        <v>1171032</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Validation Report</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Costa Rica ERPD EN_Oct24-2018_clean</t>
+          <t>2017-2021 TREES-Validation-Report-Costa Rica_Final_2026-06-15</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2026-06-17</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Concept</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Costa Rica ERPD EN_Oct24-2018_clean</t>
+          <t>TREES-Concept-Final Submission Letter 2020</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2020-12-21</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Concept</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>costa_rica_2sd_ermr_final_clean_11-jul-2024_final_0</t>
+          <t>TREES-Concept-Final-Guyana 2020</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2020-12-21</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>costa_rica_2sd_ermr_final_clean_11-jul-2024_final_0</t>
+          <t>2016-2020 CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Monitoring Report - Verified</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>costa_rica_2sd_ermr_final_clean_11-jul-2024_final_0</t>
+          <t>2016-2020 TREES-Monitoring-Report-Guyana Verified</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Registration Document - Validated</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_final_0</t>
+          <t>2016-2020 TREES-Registration-Document-Guyana Validated</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Validation Report</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_final_0</t>
+          <t>2016-2020 TREES-Validation-Report-Final</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Opinion</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_final_0</t>
+          <t>2016-2020 TREES-Verification-Opinion-Final</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Report</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_may2024_final</t>
+          <t>2016-2020 TREES-Verification-Report-Final</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2022-12-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Monitoring Report - Verified</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_may2024_final</t>
+          <t>2021 TREES-Monitoring-Report-Guyana Verified</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2023-12-30</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Opinion</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_may2024_final</t>
+          <t>2021 TREES-Verification-Opinion-Final 20231228</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2023-12-30</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Report</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>fcpf_costa_rica_er_program_vr1_adjustment_v1.1_05072024</t>
+          <t>2021 TREES-Verification-Report-Final 20231228</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2023-12-30</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Registration Document - Validated</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>fcpf_costa_rica_er_program_vr1_adjustment_v1.1_05072024</t>
+          <t>2021-2025 TREES-Registration-Document-Guyana Validated</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2023-12-30</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Validation Report</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>fcpf_costa_rica_er_program_vr1_adjustment_v1.1_05072024</t>
+          <t>2021-2025 TREES-Validation-Report-Final 20231228</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2023-12-30</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Annual Report to UNFCCC reporting Corresponding Adjustment</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>fcpf_costa_rica_er_program_vr2_v1.3_20092024</t>
+          <t>2021 Annual Report to UNFCCC reporting Corresponding Adjustment</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2024-02-21</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Host Country Letter of Authorization</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>fcpf_costa_rica_er_program_vr2_v1.3_20092024</t>
+          <t>2021 Host Country Letter of Authorization</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2024-02-21</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>fcpf_costa_rica_er_program_vr2_v1.3_20092024</t>
+          <t>2021 CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2024-02-28</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>validation_report_costa_rica_er_prgm_fcpf_v1.1</t>
+          <t>2016-2020 Guyana ART Workbook</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2024-06-06</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>validation_report_costa_rica_er_prgm_fcpf_v1.1</t>
+          <t>2021 Guyana ART Workbook</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2024-06-06</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Monitoring Report - Verified</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>validation_report_costa_rica_er_prgm_fcpf_v1.1</t>
+          <t>2022 TREES-Monitoring-Report-Guyana Verified</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-01-14</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Opinion</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>verification_report_costa_rica_er_prgm_fcpf_v1.1_0</t>
+          <t>2022 TREES-Verification-Opinion-Final</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-01-14</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Report</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>verification_report_costa_rica_er_prgm_fcpf_v1.1_0</t>
+          <t>2022 TREES-Verification-Report-Final</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-01-14</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ART0126</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>100000</v>
+        <v>62003028</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Annual Report to UNFCCC reporting Corresponding Adjustment</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>verification_report_costa_rica_er_prgm_fcpf_v1.1_0</t>
+          <t>2022 Annual Report to UNFCCC reporting Corresponding Adjustment</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2025-03-17</t>
+          <t>2025-02-21</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00005-TRA621-20260226</t>
+          <t>2022 CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-02-21</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00005-TRA621-20260226</t>
+          <t>2022 Guyana ART Workbook</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-02-21</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Host Country Letter of Authorization</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00005-TRA621-20260226</t>
+          <t>2022 Host Country Letter of Authorization</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-02-21</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Monitoring Report - Verified</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Program Documentation</t>
+          <t>2023 TREES-Monitoring-Report-Guyana-Verified</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-19</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Opinion</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Program Documentation</t>
+          <t>2023 TREES-Verification-Opinion-Final</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-20</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Verification Report</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Program Documentation</t>
+          <t>2023 TREES-Verification-Report-Final</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2025-12-20</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>190422-ERPD RCI FV</t>
+          <t>2023 Guyana ART Workbook</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-01-16</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Annual Report to UNFCCC reporting Corresponding Adjustment</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>190422-ERPD RCI FV</t>
+          <t>2023 Annual Report to UNFCCC reporting Corresponding Adjustment</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>190422-ERPD RCI FV</t>
+          <t>2023 CORSIA MRV Commitment</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>Host Country Letter of Authorization</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>GovernmentcommitmentletterwithrespecttoExcessERs-French</t>
+          <t>2023 Host Country Letter of Authorization</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-03</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0102</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Guyana</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>429590</v>
+        <v>62003028</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FCPF Supporting Documents</t>
+          <t>TREES Monitoring Report - Public Comment</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>GovernmentcommitmentletterwithrespecttoExcessERs-French</t>
+          <t>2024-TREES-Monitoring-Report-Guyana Public Comment</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-02-20</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -1699,28 +1699,28 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>GovernmentcommitmentletterwithrespecttoExcessERs-French</t>
+          <t>CATS Cancellation Certificate CAN00004-TRA242-20241127</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2024-12-03</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -1729,28 +1729,28 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>civ_fcpf_2nd_er-mr_final_incl_annexes</t>
+          <t>Program Documentation</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2024-12-03</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -1759,28 +1759,28 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>civ_fcpf_2nd_er-mr_final_incl_annexes</t>
+          <t>Costa Rica ERPD EN_Oct24-2018_clean</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -1789,28 +1789,28 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>civ_fcpf_2nd_er-mr_final_incl_annexes</t>
+          <t>costa_rica_2sd_ermr_final_clean_11-jul-2024_final_0</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -1819,28 +1819,28 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>courrier_d_avis-de_non-responsabilite_du_fiduciaire_a_l_egard_des_reductions_d_emissions_excedentaires</t>
+          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_final_0</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -1849,28 +1849,28 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>courrier_d_avis-de_non-responsabilite_du_fiduciaire_a_l_egard_des_reductions_d_emissions_excedentaires</t>
+          <t>costa_rica_fcpf_er_monitoring_report_1st_rp_may2024_final</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -1879,28 +1879,28 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>courrier_d_avis-de_non-responsabilite_du_fiduciaire_a_l_egard_des_reductions_d_emissions_excedentaires</t>
+          <t>fcpf_costa_rica_er_program_vr1_adjustment_v1.1_05072024</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -1909,28 +1909,28 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>validation_report_civ_1.5_23012024</t>
+          <t>fcpf_costa_rica_er_program_vr2_v1.3_20092024</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -1939,28 +1939,28 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>validation_report_civ_1.5_23012024</t>
+          <t>validation_report_costa_rica_er_prgm_fcpf_v1.1</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ART0130</t>
+          <t>ART0126</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
+          <t>Costa Rica FCPF REDD+ Emission Reductions Program</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>429590</v>
+        <v>100000</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>validation_report_civ_1.5_23012024</t>
+          <t>verification_report_costa_rica_er_prgm_fcpf_v1.1_0</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2025-03-17</t>
         </is>
       </c>
     </row>
@@ -1999,12 +1999,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>verification_report_civ_2nd_ermr_final</t>
+          <t>CATS Cancellation Certificate CAN00005-TRA621-20260226</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2029,12 +2029,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>verification_report_civ_2nd_ermr_final</t>
+          <t>Program Documentation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-04-03</t>
+          <t>2026-03-09</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>verification_report_civ_2nd_ermr_final</t>
+          <t>190422-ERPD RCI FV</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00007-TRA647-20260504</t>
+          <t>GovernmentcommitmentletterwithrespecttoExcessERs-French</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2119,12 +2119,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00007-TRA647-20260504</t>
+          <t>civ_fcpf_2nd_er-mr_final_incl_annexes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
@@ -2149,102 +2149,102 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate CAN00007-TRA647-20260504</t>
+          <t>courrier_d_avis-de_non-responsabilite_du_fiduciaire_a_l_egard_des_reductions_d_emissions_excedentaires</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ART0131</t>
+          <t>ART0130</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
+          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>1669630</v>
+        <v>429590</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate</t>
+          <t>FCPF Supporting Documents</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate 2019 2020 CAN00009-TRA720-20260609</t>
+          <t>validation_report_civ_1.5_23012024</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ART0131</t>
+          <t>ART0130</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
+          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1669630</v>
+        <v>429590</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate</t>
+          <t>FCPF Supporting Documents</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate 2019 2020 CAN00009-TRA720-20260609</t>
+          <t>verification_report_civ_2nd_ermr_final</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ART0131</t>
+          <t>ART0130</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
+          <t>Cote d'Ivoire Tai National Park Area Emission Reductions Program</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>1669630</v>
+        <v>429590</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate</t>
+          <t>FCPF Supporting Documents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>CATS Cancellation Certificate 2019 2020 CAN00009-TRA720-20260609</t>
+          <t>CATS Cancellation Certificate CAN00007-TRA647-20260504</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-05-06</t>
         </is>
       </c>
     </row>
@@ -2273,66 +2273,6 @@
         </is>
       </c>
       <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>ART0131</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>1669630</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>CATS Cancellation Certificate</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>CATS Cancellation Certificate 2019 2020 CAN00009-TRA720-20260609</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>2026-07-10</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>ART0131</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Democratic Republic of Congo Mai-Ndombe FCPF Emission Reductions Program</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
-        <v>1669630</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>CATS Cancellation Certificate</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>CATS Cancellation Certificate 2019 2020 CAN00009-TRA720-20260609</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
         <is>
           <t>2026-07-10</t>
         </is>
